--- a/processo_2/synthetic_proposals/PROPOSTA_038/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_038/ficha_pontuacao.xlsx
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,28 +804,20 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>6412-5073</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1015-1146</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -861,13 +853,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -947,13 +939,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -966,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -989,7 +981,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1039,13 +1031,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29" t="inlineStr"/>
     </row>
@@ -1058,7 +1050,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1083,7 +1075,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,7 +1118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1149,7 +1141,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1195,7 +1187,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1218,17 +1210,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
@@ -1241,7 +1233,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1264,7 +1256,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1287,17 +1279,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1310,7 +1302,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1333,7 +1325,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1551,7 +1543,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,7 +1566,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1620,17 +1612,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1643,7 +1635,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1660,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1715,13 +1707,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
@@ -1807,13 +1799,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
@@ -1830,13 +1822,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -1851,7 +1843,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1866,7 +1858,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>19</v>
+        <v>23.5</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
